--- a/hiring_companies_2026-10-31.xlsx
+++ b/hiring_companies_2026-10-31.xlsx
@@ -477,7 +477,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Indian Creations Corp</t>
+          <t>The Edson Agency</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -492,22 +492,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Shopify Website Designer &amp; Developer for Handmade Brand</t>
+          <t>Remote Sales Representative</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7164943953337303535</t>
+          <t>https://jooble.org/jdp/-6356946347937106590</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Indian+Creations+Corp</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Edson+Agency</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fluence International, Inc.</t>
+          <t>The Schnitzer Agency</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Remote (Worldwide)</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,22 +539,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Full-Stack Developer</t>
+          <t>Remote Sales Agent - For Car Sales &amp; Commission Pros, Leads Provided</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/full-stack-developer-2091165</t>
+          <t>https://jooble.org/jdp/3588654371810519925</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Fluence+International%2C+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Schnitzer+Agency</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -564,14 +564,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>job link live</t>
+          <t>job link unknown</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Excitingtravelnow</t>
+          <t>General Motors</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -586,22 +586,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Remote Luxury Travel Experience Designer</t>
+          <t>Buick GMC District Sales Manager - Cape Girardeau</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2888704861171868657</t>
+          <t>https://jooble.org/jdp/3181414529683982004</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Excitingtravelnow</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=General+Motors</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -618,12 +618,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ala Carte Entertainment Group</t>
+          <t>The Wood Agency Life</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -633,22 +633,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Graphic Designer</t>
+          <t>Work-From-Home Sales Specialist</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/558260608202830739</t>
+          <t>https://jooble.org/jdp/-7240299807531193251</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Ala+Carte+Entertainment+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Wood+Agency+Life</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -665,7 +665,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sweet Carolina Travels</t>
+          <t>Valor Payments</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -680,22 +680,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Remote Client Support Representative | Remote Travel Experience Designer</t>
+          <t>National Sales Manager</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/5449336265970423160</t>
+          <t>https://jooble.org/jdp/-358945469409715413</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Sweet+Carolina+Travels</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Valor+Payments</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Exciting Travel Now</t>
+          <t>MotorMate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -727,22 +727,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Remote Africa Safari and Culture Experience Designer</t>
+          <t>Freight Sales Agent - Freight Division (Commission, Remote US)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6608197372609691943</t>
+          <t>https://jooble.org/jdp/-4163255358836094364</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Exciting+Travel+Now</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=MotorMate</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IQ Mediengruppe LLC</t>
+          <t>Salesfolks</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -774,22 +774,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IQ Media Agent (m/w/d) - 100% Remote Nebenjob / Zusatzverdienst</t>
+          <t>B2B Sales Representative</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7456273658181660463</t>
+          <t>https://jooble.org/jdp/2007414634762219108</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=IQ+Mediengruppe+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Salesfolks</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>National Association of State Departments of Agriculture</t>
+          <t>GPAC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Remote Part-Time Field &amp; Phone Enumerator</t>
+          <t>Signage Sales Rep - Exterior &amp; Interior Signage Programs (Remote)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7532088770976179498</t>
+          <t>https://jooble.org/jdp/4661843765444112885</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=National+Association+of+State+Departments+of+Agriculture</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=GPAC</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sunray IT Inc</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -868,22 +868,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Senior OCI Cloud Architect</t>
+          <t>Sales Executive - Commercial Auto</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/5906370097701704473</t>
+          <t>https://jooble.org/jdp/-3435322682997897644</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Sunray+IT+Inc</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Kemper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -900,12 +900,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Promerch</t>
+          <t>N8n</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -915,22 +915,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Independent Sales Consultant - Automotive Vehicle Protection</t>
+          <t>Engineering Manager | Remote | Europe | Low-touch Customer Success Manager (Remote - EMEA) | Manager, Customer Success (Remote - EMEA)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3050766371287530075</t>
+          <t>https://jooble.org/jdp/1013414707473602247</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Promerch</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=N8n</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DSI Groups</t>
+          <t>MasterClass</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -962,22 +962,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sales Specialist — Insurance Background</t>
+          <t>Social Media Manager, Immediate Start</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2894448981827878019</t>
+          <t>https://jooble.org/jdp/-4585367747249773061</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=DSI+Groups</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=MasterClass</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -994,7 +994,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MADEO</t>
+          <t>Genesys</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1009,22 +1009,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Senior Web Designer</t>
+          <t>Lead Software Engineer, CRM and Integrations</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2504855219931714239</t>
+          <t>https://jooble.org/jdp/-7717472795597123071</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=MADEO</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Genesys</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dreamers of Day</t>
+          <t>Brookfield Properties</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1056,22 +1056,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Senior Web Designer</t>
+          <t>Residential Market Specialist</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8565397452905559617</t>
+          <t>https://jooble.org/jdp/5344604761691220832</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Dreamers+of+Day</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Brookfield+Properties</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MyOutDesk, LLC</t>
+          <t>Bella+Canvas</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1103,22 +1103,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Brand &amp; Web Designer: Conversion-Driven Visual Artist</t>
+          <t>Brand Engagement Specialist (New York, New Jersey)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2082798852789696297</t>
+          <t>https://jooble.org/jdp/748500208830495251</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=MyOutDesk%2C+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Bella%2BCanvas</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Viget</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Product &amp; Web Designer Intern (2027)</t>
+          <t>Field Sales Sr Officer - C12 - Telecommuter</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7630781959470126199</t>
+          <t>https://jooble.org/jdp/-1388885118149723082</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Viget</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Citi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>Ladder</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sr. Digital Visual Designer</t>
+          <t>DevSecOps/AppSec Engineer</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7320723561292902136</t>
+          <t>https://jooble.org/jdp/-7601143066018183936</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Extractable</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Ladder</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Impleo</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,22 +1244,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Remote 3D Animation Designer (Contract)</t>
+          <t>Command Center Solutions Services (CCSS) Engineering Organization - Software Engineer</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2630734852131296733</t>
+          <t>https://jooble.org/jdp/-4736593263205368727</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Impleo</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Motorola+Solutions</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1276,12 +1276,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Zack D. Films LLC</t>
+          <t>Transportation Insight</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1291,22 +1291,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Contract 3D Animator for High-Impact Shorts</t>
+          <t>Remote : Senior Solution Engineer</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8008321125920895800</t>
+          <t>https://jooble.org/jdp/-5796207218440691998</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Zack+D.+Films+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Transportation+Insight</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1323,7 +1323,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RethinkFirst</t>
+          <t>Form3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Social Media Specialist</t>
+          <t>Senior Digital Marketing Manager</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-3106277355300413848</t>
+          <t>https://jooble.org/jdp/4935551733431472952</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=RethinkFirst</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Form3</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1370,7 +1370,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Educo LLC</t>
+          <t>Buechel Stone</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1385,22 +1385,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Video Editor</t>
+          <t>Territory Sales Representative</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6694034428283635956</t>
+          <t>https://jooble.org/jdp/1227390752977077155</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Educo+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Buechel+Stone</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Gannett</t>
+          <t>CD PROJEKT RED</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1432,22 +1432,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Local News Editor - Sarasota Tribune</t>
+          <t>Senior Rendering Engineer</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/662818734854484338</t>
+          <t>https://jooble.org/jdp/-1532920671891556391</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Gannett</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=CD+PROJEKT+RED</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1464,7 +1464,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DreamThree, Inc</t>
+          <t>MissionTek Advisors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1479,22 +1479,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Short Form Video Editor</t>
+          <t>SQL Developer</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8072899555108578749</t>
+          <t>https://jooble.org/jdp/1028469190134775671</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=DreamThree%2C+Inc</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=MissionTek+Advisors</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>The Christian and Missionary Alliance</t>
+          <t>Afterman Software</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1526,22 +1526,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Communications Director</t>
+          <t>Senior .NET Engineer (Banking)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8464263928504207098</t>
+          <t>https://jooble.org/jdp/5319560793693365054</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Christian+and+Missionary+Alliance</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Afterman+Software</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1558,7 +1558,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NYC Service</t>
+          <t>Searchlight</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1573,22 +1573,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Social Media Coordinator</t>
+          <t>Senior Vice President Marketing</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2238587121829820353</t>
+          <t>https://jooble.org/jdp/-1805568591421818470</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=NYC+Service</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Searchlight</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1605,7 +1605,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VivoSense, Inc.</t>
+          <t>Snipp Interactive</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1620,22 +1620,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Senior Content Marketing Manager</t>
+          <t>Remote Senior Customer Experience UX &amp; Creative Designer</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/5730931950570920447</t>
+          <t>https://jooble.org/jdp/1476576547527432583</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=VivoSense%2C+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Snipp+Interactive</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1652,7 +1652,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Business of Home</t>
+          <t>Saviance</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1667,22 +1667,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Social Media Manager</t>
+          <t>UX Designer</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4512772164418418219</t>
+          <t>https://jooble.org/jdp/-4559408149397368804</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Business+of+Home</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Saviance</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1699,12 +1699,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Guardian Dentistry Partners</t>
+          <t>Warmhlee</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1714,22 +1714,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Remote Social Media Coordinator for Dental Network | Social Media Coordinator</t>
+          <t>Remote 3D AI Animator — Tell Stories with AI-Driven Motion</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/437180026072159184</t>
+          <t>https://jooble.org/jdp/3622321162883763294</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Guardian+Dentistry+Partners</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Warmhlee</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1746,7 +1746,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Scott Frindell - State Farm Agent</t>
+          <t>Xad Technologies</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1761,22 +1761,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Intern - State Farm Agent Team Member</t>
+          <t>UI/UX Designer - Remote</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-3935218330935989524</t>
+          <t>https://jooble.org/jdp/-2266141499635135382</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Scott+Frindell+-+State+Farm+Agent</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Xad+Technologies</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1793,12 +1793,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hercules</t>
+          <t>Clipt</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1808,22 +1808,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Social Media Manager</t>
+          <t>Graphic Designer | Motion Graphics Editor</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3985306437594637797</t>
+          <t>https://jooble.org/jdp/3670893143887339455</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hercules</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Clipt</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fairmarkit</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1855,22 +1855,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Marketing Executive - Remote</t>
+          <t>Senior UX Designer</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8118790026471779237</t>
+          <t>https://jooble.org/jdp/-5179814789710757255</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Fairmarkit</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=World+Wide+Technology</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1887,12 +1887,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>The Lawfare Project</t>
+          <t>Sweetcarolinatravels</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1902,22 +1902,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Social Media Manager</t>
+          <t>Remote Travel Experience Designer</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8765050034417603216</t>
+          <t>https://jooble.org/jdp/7028860635981006565</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Lawfare+Project</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Sweetcarolinatravels</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1934,7 +1934,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Knit</t>
+          <t>National Agents Alliance - The Alliance</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1949,22 +1949,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Director, Growth Marketing</t>
+          <t>Social Media Assistant</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3909530428839569037</t>
+          <t>https://jooble.org/jdp/-1307334220262994882</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Knit</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=National+Agents+Alliance+-+The+Alliance</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Law Offices of Sabrina Li, P.C.</t>
+          <t>Emery Sapp &amp; Sons</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1996,22 +1996,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Head of Marketing</t>
+          <t>Videographer</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-3322451889752797449</t>
+          <t>https://jooble.org/jdp/-5062074078806983516</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Law+Offices+of+Sabrina+Li%2C+P.C.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Emery+Sapp+%26+Sons</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2028,7 +2028,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Business Solutions Partners</t>
+          <t>Council on Foreign Relations</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2043,22 +2043,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VP of Marketing</t>
+          <t>Managing Editor, Think Global Health</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8289512124629845419</t>
+          <t>https://jooble.org/jdp/-6876685983080629077</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Business+Solutions+Partners</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Council+on+Foreign+Relations</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2075,7 +2075,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JVM Lending</t>
+          <t>Creative Ave Co.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Director of Marketing</t>
+          <t>Social Media Coordinator</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-3554726496888030763</t>
+          <t>https://jooble.org/jdp/-7365502349966293109</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=JVM+Lending</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Creative+Ave+Co.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2122,7 +2122,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Maxaix</t>
+          <t>UW Medicine</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2137,22 +2137,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Digital Marketing Executive</t>
+          <t>Senior Writer, Harborview Medical Center - UW Medicine, Strategic Communications</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-6933605324222396315</t>
+          <t>https://jooble.org/jdp/3949543549191810916</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Maxaix</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=UW+Medicine</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2169,7 +2169,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>d97dc9de-74cf-418a-8f44-cd8ba295367f</t>
+          <t>National Women's Soccer League</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2184,22 +2184,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Senior Salesforce Platform Engineer (Remote)</t>
+          <t>Digital Video Editor</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/607351289931905903</t>
+          <t>https://jooble.org/jdp/-5816963507736804962</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=d97dc9de-74cf-418a-8f44-cd8ba295367f</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=National+Women%27s+Soccer+League</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2216,7 +2216,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>brk tech, A Berkshire Hathaway Group Company</t>
+          <t>Prince George's Community College</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2231,22 +2231,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Principal Messaging Platform Engineer</t>
+          <t>Adjunct Faculty, ESL</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/9073375931723259550</t>
+          <t>https://jooble.org/jdp/-7352359357811153538</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=brk+tech%2C+A+Berkshire+Hathaway+Group+Company</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Prince+George%27s+Community+College</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2263,7 +2263,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2278,22 +2278,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Senior Manager, Salesforce Business Intelligence Developer-Commercial</t>
+          <t>TikTok Shop &amp; Social Media Coordinator</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7931111045705610025</t>
+          <t>https://jooble.org/jdp/-4034008353761314959</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CVS+Health</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=PSD</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2310,7 +2310,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Verisys</t>
+          <t>KittySpout</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2325,22 +2325,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer (AWS) (copy)</t>
+          <t>Junior Media Buyer - Meta Ads</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-247013470566475954</t>
+          <t>https://jooble.org/jdp/-8723470864673191445</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Verisys</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=KittySpout</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Reunion Marketing</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2372,22 +2372,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Principal Software Engineer - Emerging Technology &amp; AI - Remote</t>
+          <t>Regional Sales Director - Great Lakes Region</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3925783063210447918</t>
+          <t>https://jooble.org/jdp/8230710050730020740</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CSAA+Insurance+Group%2C+a+AAA+Insurer</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Reunion+Marketing</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2404,7 +2404,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tripoint Solutions LLC</t>
+          <t>Team Velocity</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2419,22 +2419,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Remote Performance Marketing Strategist</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7769565283611058349</t>
+          <t>https://jooble.org/jdp/-3918565733659521333</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Tripoint+Solutions+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Team+Velocity</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Taego</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2466,22 +2466,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Solution Engineer - ValueOps | Solutions Engineering (Remote)</t>
+          <t>Marketing Executive</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7624343633417580775</t>
+          <t>https://jooble.org/jdp/-4104082696414887313</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Broadcom</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Taego</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2498,7 +2498,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>c968050c-15a9-468b-acaf-b26b765aff76</t>
+          <t>Scalejet</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2513,22 +2513,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Remote : Senior Solution Engineer | Solutions Engineer</t>
+          <t>Senior Amazon PPC Strategist</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5263678631533858225</t>
+          <t>https://jooble.org/jdp/5568787226837322000</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=c968050c-15a9-468b-acaf-b26b765aff76</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Scalejet</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2545,7 +2545,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nava PBC</t>
+          <t>GuidePoint Security</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2560,22 +2560,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Senior Engineering Manager (Java)</t>
+          <t>DevSecOps Presales Solutions Engineer - Mid-Atlantic region (Remote in VA, MD, PA, NC, DE, NJ, or DC)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-6710795714845024792</t>
+          <t>https://jooble.org/jdp/-1506507865006046120</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Nava+PBC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=GuidePoint+Security</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2592,7 +2592,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mark43</t>
+          <t>Creative Information Technology, Inc.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2607,22 +2607,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Fully Remote</t>
+          <t>SR JAVA DEVELOPER - Remote / Onsite - McLean, VA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2403857721189357732</t>
+          <t>https://jooble.org/jdp/5993497161437641643</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Mark43</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Creative+Information+Technology%2C+Inc.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2639,7 +2639,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CONCEPT SOLUTIONS LLC</t>
+          <t>Catapult Federal Services</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2654,22 +2654,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Database Engineer - PostgreSQL (AWS RDS)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8126674082116631614</t>
+          <t>https://jooble.org/jdp/6879604421699008618</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CONCEPT+SOLUTIONS+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Catapult+Federal+Services</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2686,7 +2686,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ChaosTrack</t>
+          <t>OpenKrill</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2701,22 +2701,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Remote Sales Consultant</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6527257204456134642</t>
+          <t>https://jooble.org/jdp/8643536788651071536</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=ChaosTrack</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=OpenKrill</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Omni Inclusive</t>
+          <t>Promoted2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2748,22 +2748,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>C++ Developer</t>
+          <t>Remote Sales Executive</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4059777758417023539</t>
+          <t>https://jooble.org/jdp/7588292897276050425</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Omni+Inclusive</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Promoted2</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2780,7 +2780,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cetera</t>
+          <t>Jeld-Wen Inc.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2795,22 +2795,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Retirement Plan Sales Consultant | Sales Consultant - Remote</t>
+          <t>Remote Sales Representative Full Time</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7971725331079594178</t>
+          <t>https://jooble.org/jdp/1493378439842052934</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Cetera</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Jeld-Wen+Inc.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
